--- a/TRANSFORMATION_INFO.xlsx
+++ b/TRANSFORMATION_INFO.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t xml:space="preserve">diff+seasonal_diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STL</t>
   </si>
   <si>
     <t xml:space="preserve">sa_diff</t>
@@ -775,15 +778,15 @@
         <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
@@ -828,10 +831,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -840,7 +843,7 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -873,7 +876,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
@@ -890,7 +893,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -907,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -919,12 +922,12 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -941,7 +944,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -958,7 +961,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -975,7 +978,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -992,7 +995,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -1009,7 +1012,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
@@ -1054,7 +1057,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -1071,7 +1074,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
@@ -1088,7 +1091,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -1105,10 +1108,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -1117,12 +1120,12 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -1167,7 +1170,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
@@ -1184,10 +1187,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -1196,12 +1199,12 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1218,7 +1221,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -1263,7 +1266,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1280,10 +1283,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -1292,12 +1295,12 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1314,7 +1317,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -1331,7 +1334,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -1348,7 +1351,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -1365,7 +1368,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -1382,10 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
@@ -1394,7 +1397,7 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1427,7 +1430,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1444,10 +1447,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -1456,15 +1459,15 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -1473,15 +1476,15 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -1490,15 +1493,15 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -1507,15 +1510,15 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -1524,24 +1527,24 @@
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1574,44 +1577,44 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -1620,15 +1623,15 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -1637,15 +1640,15 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -1654,7 +1657,7 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1687,10 +1690,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -1699,15 +1702,15 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -1716,15 +1719,15 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -1733,15 +1736,15 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -1750,7 +1753,7 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1783,10 +1786,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -1795,15 +1798,15 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -1812,15 +1815,15 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -1829,7 +1832,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
